--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_397_R44.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_397_R44.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5028</v>
+        <v>4.3073</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6216</v>
+        <v>3.2322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8812</v>
+        <v>1.0751</v>
       </c>
       <c r="G2" t="n">
         <v>0.8759</v>
@@ -610,13 +610,13 @@
         <v>3.4121</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.415</v>
+        <v>-0.6105</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.323</v>
+        <v>0.2876</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.092</v>
+        <v>-0.8981</v>
       </c>
       <c r="V2" t="n">
         <v>3.587</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2269</v>
+        <v>0.9139</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7555</v>
+        <v>1.107</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.1931</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.5295</v>
+        <v>0.4018</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.157</v>
+        <v>-1.417</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3725</v>
+        <v>1.8187</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.5206</v>
+        <v>0.9093</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4875</v>
+        <v>-0.6593</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0332</v>
+        <v>1.5687</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0088</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6695</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3393</v>
+        <v>0.2501</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3648</v>
+        <v>0.6824</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.2275</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5923</v>
+        <v>0.9099</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9147</v>
+        <v>-0.012</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7784</v>
+        <v>0.4251</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1363</v>
+        <v>-0.4371</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4768</v>
+        <v>-0.1583</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7253</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2485</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7478</v>
+        <v>0.7819</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7615</v>
+        <v>0.8602</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0137</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7174</v>
@@ -766,13 +766,13 @@
         <v>2.9572</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3064</v>
+        <v>-0.2723</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2278</v>
+        <v>0.3265</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5342</v>
+        <v>-0.5988</v>
       </c>
       <c r="V4" t="n">
         <v>1.4068</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6757</v>
+        <v>0.5337</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.2886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0915</v>
+        <v>-0.7549</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0355</v>
+        <v>-2.5295</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0503</v>
+        <v>-2.157</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0148</v>
+        <v>-0.3725</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2489</v>
+        <v>-1.5206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0173</v>
+        <v>-1.4875</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2317</v>
+        <v>-0.0332</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2844</v>
+        <v>-1.0088</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0675</v>
+        <v>-0.6695</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2169</v>
+        <v>-0.3393</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.3648</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2275</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2275</v>
+        <v>1.5923</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.2215</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5628</v>
+        <v>0.3114</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1484</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4768</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7253</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6337</v>
+        <v>0.4943</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7299</v>
+        <v>0.4675</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0961</v>
+        <v>0.0268</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4018</v>
+        <v>-0.0355</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.417</v>
+        <v>-0.0503</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8187</v>
+        <v>0.0148</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9093</v>
+        <v>0.2489</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6593</v>
+        <v>0.0173</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5687</v>
+        <v>0.2317</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.2844</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.0675</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2501</v>
+        <v>-0.2169</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6824</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.2275</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2921</v>
+        <v>0.5298</v>
       </c>
       <c r="T6" t="n">
-        <v>0.048</v>
+        <v>0.446</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3401</v>
+        <v>0.0837</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6885</v>
+        <v>-0.0512</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2093</v>
+        <v>3.9475</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4792</v>
+        <v>-3.9987</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3468</v>
+        <v>1.5085</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9323</v>
+        <v>0.7966</v>
       </c>
       <c r="I7" t="n">
-        <v>2.279</v>
+        <v>0.7119</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8168</v>
+        <v>3.9081</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9009</v>
+        <v>2.4844</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7177</v>
+        <v>1.4237</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4701</v>
+        <v>-2.3996</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0314</v>
+        <v>-1.6878</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5614</v>
+        <v>-0.7119</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1374</v>
+        <v>0.4549</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.7297</v>
+        <v>-1.3648</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5923</v>
+        <v>1.8198</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.443</v>
+        <v>-0.7662</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4551</v>
+        <v>0.1558</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.898</v>
+        <v>-0.922</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5451</v>
+        <v>-1.2485</v>
       </c>
       <c r="W7" t="n">
         <v>1.2485</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7034</v>
+        <v>-2.4969</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9275</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2651</v>
+        <v>-0.2542</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1927</v>
+        <v>-0.4792</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5085</v>
+        <v>0.3468</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7966</v>
+        <v>-1.9323</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7119</v>
+        <v>2.279</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9081</v>
+        <v>0.8168</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4844</v>
+        <v>-0.9009</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4237</v>
+        <v>1.7177</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3996</v>
+        <v>-0.4701</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6878</v>
+        <v>-1.0314</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7119</v>
+        <v>0.5614</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4549</v>
+        <v>-1.1374</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3648</v>
+        <v>-2.7297</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8198</v>
+        <v>1.5923</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6425</v>
+        <v>-0.4879</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5266</v>
+        <v>0.4102</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1159</v>
+        <v>-0.898</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2485</v>
+        <v>0.5451</v>
       </c>
       <c r="W8" t="n">
         <v>1.2485</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4969</v>
+        <v>-0.7034</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0843</v>
+        <v>-1.3698</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1064</v>
+        <v>-0.4566</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9779</v>
+        <v>-0.9132</v>
       </c>
       <c r="G9" t="n">
         <v>-1.286</v>
@@ -1156,13 +1156,13 @@
         <v>0.2275</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6777</v>
+        <v>0.3921</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.2844</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0431</v>
+        <v>0.1077</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7034</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4791</v>
+        <v>-2.6572</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3773</v>
+        <v>-2.1676</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1018</v>
+        <v>-0.4897</v>
       </c>
       <c r="G10" t="n">
         <v>-4.5974</v>
@@ -1234,13 +1234,13 @@
         <v>2.0473</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5732</v>
+        <v>0.3951</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6644</v>
+        <v>0.8742</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0912</v>
+        <v>-0.4791</v>
       </c>
       <c r="V10" t="n">
         <v>1.0901</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.9421</v>
+        <v>-6.4767</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.511</v>
+        <v>-4.4335</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4311</v>
+        <v>-2.0432</v>
       </c>
       <c r="G11" t="n">
         <v>-6.6261</v>
@@ -1312,13 +1312,13 @@
         <v>2.2747</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.5908</v>
+        <v>-1.1254</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1252</v>
+        <v>-0.0477</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4655</v>
+        <v>-1.0777</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5451</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3346</v>
+        <v>-4.257200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.513800000000001</v>
+        <v>3.591099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.8485</v>
+        <v>-7.8484</v>
       </c>
       <c r="G12" t="n">
         <v>-13.6589</v>
@@ -1360,7 +1360,7 @@
         <v>-15.19</v>
       </c>
       <c r="I12" t="n">
-        <v>1.530799999999998</v>
+        <v>1.530799999999999</v>
       </c>
       <c r="J12" t="n">
         <v>-0.6766000000000001</v>
@@ -1390,16 +1390,16 @@
         <v>17.0606</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.813000000000001</v>
+        <v>-1.7358</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3963</v>
+        <v>3.4735</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.2091</v>
+        <v>-5.2093</v>
       </c>
       <c r="V12" t="n">
-        <v>5.450500000000002</v>
+        <v>5.4505</v>
       </c>
       <c r="W12" t="n">
         <v>12.1681</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.3813</v>
+        <v>8.1714</v>
       </c>
       <c r="E13" t="n">
-        <v>8.9602</v>
+        <v>5.6916</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4211</v>
+        <v>2.4798</v>
       </c>
       <c r="G13" t="n">
         <v>4.6634</v>
@@ -1468,13 +1468,13 @@
         <v>1.8198</v>
       </c>
       <c r="S13" t="n">
-        <v>5.766</v>
+        <v>2.5561</v>
       </c>
       <c r="T13" t="n">
-        <v>5.2203</v>
+        <v>1.9517</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5457</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.4068</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8599</v>
+        <v>3.7374</v>
       </c>
       <c r="E14" t="n">
-        <v>6.22</v>
+        <v>4.9359</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3601</v>
+        <v>-1.1985</v>
       </c>
       <c r="G14" t="n">
         <v>2.1556</v>
@@ -1546,13 +1546,13 @@
         <v>1.5923</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4305</v>
+        <v>1.308</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4665</v>
+        <v>1.1824</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0361</v>
+        <v>0.1256</v>
       </c>
       <c r="V14" t="n">
         <v>-1.3185</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9121</v>
+        <v>2.0697</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2596</v>
+        <v>0.3241</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1717</v>
+        <v>1.7456</v>
       </c>
       <c r="G15" t="n">
         <v>2.2362</v>
@@ -1624,13 +1624,13 @@
         <v>1.8198</v>
       </c>
       <c r="S15" t="n">
-        <v>0.857</v>
+        <v>1.0146</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.371</v>
+        <v>0.2127</v>
       </c>
       <c r="U15" t="n">
-        <v>1.228</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8635</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2966</v>
+        <v>0.75</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.4821</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2966</v>
+        <v>1.2321</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4669</v>
+        <v>2.9399</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1556</v>
+        <v>2.7495</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3113</v>
+        <v>0.1903</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.5527</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.3112</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.2415</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4669</v>
+        <v>0.3871</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1556</v>
+        <v>1.4383</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3113</v>
+        <v>-1.0512</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2275</v>
+        <v>-1.8198</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4121</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2275</v>
+        <v>1.5923</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2395</v>
+        <v>0.2634</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.3773</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2395</v>
+        <v>-0.1139</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1583</v>
+        <v>-0.6334</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1583</v>
+        <v>-0.6334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3074</v>
+        <v>0.6549</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0717</v>
+        <v>0.3162</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3791</v>
+        <v>0.3387</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6824</v>
+        <v>1.1475</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4323</v>
+        <v>0.1391</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2501</v>
+        <v>1.0084</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6217</v>
+        <v>0.7762</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6217</v>
+        <v>-0.4159</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.1921</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0607</v>
+        <v>0.3714</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1894</v>
+        <v>0.5551</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2501</v>
+        <v>-0.1837</v>
       </c>
       <c r="P17" t="n">
         <v>-2.2747</v>
@@ -1780,28 +1780,28 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2849</v>
+        <v>0.3053</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.1796</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3496</v>
+        <v>0.1256</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4768</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0901</v>
+        <v>1.6352</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0901</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.376</v>
+        <v>0.4522</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1507</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2253</v>
+        <v>0.4522</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1475</v>
+        <v>0.4669</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1391</v>
+        <v>0.1556</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0084</v>
+        <v>0.3113</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7762</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4159</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1921</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3714</v>
+        <v>0.4669</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5551</v>
+        <v>0.1556</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1837</v>
+        <v>0.3113</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2747</v>
+        <v>0.2275</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.2275</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7256</v>
+        <v>-0.0838</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2873</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4383</v>
+        <v>-0.0838</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4768</v>
+        <v>-0.1583</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6352</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-0.1583</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8902</v>
+        <v>-0.4367</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6494</v>
+        <v>0.6048</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7592</v>
+        <v>-1.0414</v>
       </c>
       <c r="G19" t="n">
-        <v>2.9399</v>
+        <v>1.6824</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7495</v>
+        <v>1.4323</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1903</v>
+        <v>0.2501</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5527</v>
+        <v>1.6217</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3112</v>
+        <v>1.6217</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2415</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3871</v>
+        <v>0.0607</v>
       </c>
       <c r="N19" t="n">
-        <v>1.4383</v>
+        <v>-0.1894</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0512</v>
+        <v>0.2501</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8198</v>
+        <v>-2.2747</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4121</v>
+        <v>-2.2747</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5923</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3769</v>
+        <v>0.1556</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7901</v>
+        <v>0.1676</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5868</v>
+        <v>-0.012</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6334</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6334</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0039</v>
+        <v>-1.0791</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-1.0402</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3784</v>
+        <v>-0.0389</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6914</v>
+        <v>-0.4676</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0359</v>
+        <v>0.3387</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3445</v>
+        <v>-0.8063</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6402</v>
+        <v>0.2529</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6402</v>
+        <v>-0.3926</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6455</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0512</v>
+        <v>-0.7205</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3957</v>
+        <v>0.7313</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3445</v>
+        <v>-1.4518</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2275</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2275</v>
+        <v>1.3648</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6082</v>
+        <v>1.2301</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1437</v>
+        <v>0.8233</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4646</v>
+        <v>0.4068</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9318</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,22 +2047,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2967</v>
+        <v>-1.291</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9275</v>
+        <v>-0.5088</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3692</v>
+        <v>-0.7822</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8534</v>
+        <v>-0.6914</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3964</v>
+        <v>-1.0359</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4569</v>
+        <v>0.3445</v>
       </c>
       <c r="J21" t="n">
         <v>-0.6402</v>
@@ -2074,46 +2074,46 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2131</v>
+        <v>-0.0512</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2438</v>
+        <v>-0.3957</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4569</v>
+        <v>0.3445</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6824</v>
+        <v>0.2275</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6824</v>
+        <v>0.2275</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9674</v>
+        <v>0.1047</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2873</v>
+        <v>-0.0269</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6801</v>
+        <v>0.1317</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1583</v>
+        <v>-0.9318</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1583</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.908</v>
+        <v>-1.3562</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0908</v>
+        <v>-0.5773</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8171</v>
+        <v>-0.7789</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4676</v>
+        <v>-1.8534</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3387</v>
+        <v>-0.3964</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8063</v>
+        <v>-1.4569</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2529</v>
+        <v>-0.6402</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3926</v>
+        <v>-0.6402</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6455</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7205</v>
+        <v>-1.2131</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7313</v>
+        <v>0.2438</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4518</v>
+        <v>-1.4569</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9099</v>
+        <v>0.6824</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3648</v>
+        <v>0.6824</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5987</v>
+        <v>-0.027</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2273</v>
+        <v>0.0629</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3714</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9318</v>
+        <v>-0.1583</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0901</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3329</v>
+        <v>-2.4467</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5415</v>
+        <v>-1.2574</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7914</v>
+        <v>-1.1892</v>
       </c>
       <c r="G23" t="n">
         <v>1.3794</v>
@@ -2248,13 +2248,13 @@
         <v>2.0473</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.009</v>
+        <v>-0.1227</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0056</v>
+        <v>0.2785</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0034</v>
+        <v>-0.4012</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3386</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.3348</v>
+        <v>9.225900000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>8.006899999999998</v>
+        <v>8.006800000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.672</v>
+        <v>1.2193</v>
       </c>
       <c r="G24" t="n">
         <v>13.6589</v>
@@ -2302,22 +2302,22 @@
         <v>12.9825</v>
       </c>
       <c r="K24" t="n">
-        <v>7.7264</v>
+        <v>7.726400000000001</v>
       </c>
       <c r="L24" t="n">
         <v>5.2561</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6765999999999994</v>
+        <v>0.6766000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>7.463300000000001</v>
+        <v>7.4633</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.786799999999999</v>
+        <v>-6.786800000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.6867</v>
+        <v>-5.686699999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-17.0604</v>
@@ -2326,19 +2326,19 @@
         <v>11.3737</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8131</v>
+        <v>6.704299999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>5.209099999999999</v>
+        <v>5.2091</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.3961</v>
+        <v>1.4951</v>
       </c>
       <c r="V24" t="n">
         <v>-5.4506</v>
       </c>
       <c r="W24" t="n">
-        <v>6.875699999999999</v>
+        <v>6.8757</v>
       </c>
       <c r="X24" t="n">
         <v>-12.326</v>
